--- a/data/trans_orig/P1406-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P1406-Clase-trans_orig.xlsx
@@ -536,7 +536,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de úlcera de estómago en 2012</t>
+          <t>Población con diagnóstico de úlcera de estómago en 2012 (tasa de respuesta: 99,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -736,7 +736,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>7324</t>
+          <t>7438</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -751,7 +751,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -771,7 +771,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>7044</t>
+          <t>6017</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -786,7 +786,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -801,12 +801,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1028</t>
+          <t>1001</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>9215</t>
+          <t>9818</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -816,12 +816,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>0,13%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,31%</t>
         </is>
       </c>
     </row>
@@ -844,7 +844,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>429887</t>
+          <t>429773</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -859,7 +859,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>98,32%</t>
+          <t>98,3%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -879,7 +879,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>307410</t>
+          <t>308437</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -894,7 +894,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>97,76%</t>
+          <t>98,09%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -914,12 +914,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>742450</t>
+          <t>741847</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>750637</t>
+          <t>750664</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -929,12 +929,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,77%</t>
+          <t>98,69%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,86%</t>
+          <t>99,87%</t>
         </is>
       </c>
     </row>
@@ -1074,12 +1074,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1958</t>
+          <t>1892</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>11222</t>
+          <t>11300</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1089,12 +1089,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>977</t>
+          <t>968</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>13602</t>
+          <t>13382</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1129,7 +1129,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>3,96%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1144,12 +1144,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>4182</t>
+          <t>4077</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>18585</t>
+          <t>19445</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,57%</t>
         </is>
       </c>
     </row>
@@ -1187,12 +1187,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>407575</t>
+          <t>407497</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>416839</t>
+          <t>416905</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1202,12 +1202,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,32%</t>
+          <t>97,3%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,53%</t>
+          <t>99,55%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1222,12 +1222,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>324409</t>
+          <t>324629</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>337034</t>
+          <t>337043</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1237,7 +1237,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>95,98%</t>
+          <t>96,04%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1257,12 +1257,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>738223</t>
+          <t>737363</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>752626</t>
+          <t>752731</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1272,12 +1272,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,54%</t>
+          <t>97,43%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,45%</t>
+          <t>99,46%</t>
         </is>
       </c>
     </row>
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1057</t>
+          <t>1054</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>9699</t>
+          <t>9557</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1437,7 +1437,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1457,7 +1457,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>7437</t>
+          <t>6846</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1472,7 +1472,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1487,12 +1487,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2174</t>
+          <t>2231</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>13307</t>
+          <t>12876</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1502,12 +1502,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,45%</t>
         </is>
       </c>
     </row>
@@ -1530,12 +1530,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>619716</t>
+          <t>619858</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>628358</t>
+          <t>628361</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1545,7 +1545,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>98,46%</t>
+          <t>98,48%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1565,7 +1565,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>252692</t>
+          <t>253283</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -1580,7 +1580,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>97,14%</t>
+          <t>97,37%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1600,12 +1600,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>876237</t>
+          <t>876668</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>887370</t>
+          <t>887313</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1615,12 +1615,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,5%</t>
+          <t>98,55%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,76%</t>
+          <t>99,75%</t>
         </is>
       </c>
     </row>
@@ -1760,12 +1760,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>14578</t>
+          <t>14077</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>35984</t>
+          <t>33748</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1775,12 +1775,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1795,12 +1795,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>6290</t>
+          <t>5559</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>21359</t>
+          <t>21013</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1810,12 +1810,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>2,75%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1830,12 +1830,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>22919</t>
+          <t>23884</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>47977</t>
+          <t>49684</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1845,12 +1845,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,58%</t>
         </is>
       </c>
     </row>
@@ -1873,12 +1873,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1123025</t>
+          <t>1125261</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1144431</t>
+          <t>1144932</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1888,12 +1888,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,9%</t>
+          <t>97,09%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,74%</t>
+          <t>98,79%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1908,12 +1908,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>743363</t>
+          <t>743709</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>758432</t>
+          <t>759163</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1923,12 +1923,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>97,21%</t>
+          <t>97,25%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,18%</t>
+          <t>99,27%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1943,12 +1943,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1875754</t>
+          <t>1874047</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1900812</t>
+          <t>1899847</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1958,12 +1958,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,51%</t>
+          <t>97,42%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,81%</t>
+          <t>98,76%</t>
         </is>
       </c>
     </row>
@@ -2103,12 +2103,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2237</t>
+          <t>2935</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>13297</t>
+          <t>13893</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2118,12 +2118,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2138,12 +2138,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>8412</t>
+          <t>8545</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>24751</t>
+          <t>24349</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2153,12 +2153,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2173,12 +2173,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>12837</t>
+          <t>13441</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>31640</t>
+          <t>31383</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2188,12 +2188,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,47%</t>
         </is>
       </c>
     </row>
@@ -2216,12 +2216,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>497299</t>
+          <t>496703</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>508359</t>
+          <t>507661</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2231,12 +2231,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>97,4%</t>
+          <t>97,28%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,56%</t>
+          <t>99,43%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2251,12 +2251,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>735495</t>
+          <t>735897</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>751834</t>
+          <t>751701</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2266,12 +2266,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>96,74%</t>
+          <t>96,8%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>98,89%</t>
+          <t>98,88%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2286,12 +2286,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1239203</t>
+          <t>1239460</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1258006</t>
+          <t>1257402</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2301,12 +2301,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>97,51%</t>
+          <t>97,53%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,99%</t>
+          <t>98,94%</t>
         </is>
       </c>
     </row>
@@ -2446,12 +2446,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>1926</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2461,12 +2461,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2481,12 +2481,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>3228</t>
+          <t>4105</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>15239</t>
+          <t>16061</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2496,47 +2496,47 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
+          <t>0,37%</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>1,45%</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="R19" s="2" t="inlineStr">
+        <is>
+          <t>8385</t>
+        </is>
+      </c>
+      <c r="S19" s="2" t="inlineStr">
+        <is>
+          <t>3982</t>
+        </is>
+      </c>
+      <c r="T19" s="2" t="inlineStr">
+        <is>
+          <t>15303</t>
+        </is>
+      </c>
+      <c r="U19" s="2" t="inlineStr">
+        <is>
+          <t>0,61%</t>
+        </is>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
+        <is>
           <t>0,29%</t>
         </is>
       </c>
-      <c r="P19" s="2" t="inlineStr">
-        <is>
-          <t>1,38%</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="R19" s="2" t="inlineStr">
-        <is>
-          <t>8385</t>
-        </is>
-      </c>
-      <c r="S19" s="2" t="inlineStr">
-        <is>
-          <t>3344</t>
-        </is>
-      </c>
-      <c r="T19" s="2" t="inlineStr">
-        <is>
-          <t>15177</t>
-        </is>
-      </c>
-      <c r="U19" s="2" t="inlineStr">
-        <is>
-          <t>0,61%</t>
-        </is>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>0,24%</t>
-        </is>
-      </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,11%</t>
         </is>
       </c>
     </row>
@@ -2559,12 +2559,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>264956</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>266882</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2574,12 +2574,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>99,28%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2594,12 +2594,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1092930</t>
+          <t>1092108</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1104941</t>
+          <t>1104064</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2609,47 +2609,47 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>98,62%</t>
+          <t>98,55%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
+          <t>99,63%</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="inlineStr">
+        <is>
+          <t>1300</t>
+        </is>
+      </c>
+      <c r="R20" s="2" t="inlineStr">
+        <is>
+          <t>1366666</t>
+        </is>
+      </c>
+      <c r="S20" s="2" t="inlineStr">
+        <is>
+          <t>1359748</t>
+        </is>
+      </c>
+      <c r="T20" s="2" t="inlineStr">
+        <is>
+          <t>1371069</t>
+        </is>
+      </c>
+      <c r="U20" s="2" t="inlineStr">
+        <is>
+          <t>99,39%</t>
+        </is>
+      </c>
+      <c r="V20" s="2" t="inlineStr">
+        <is>
+          <t>98,89%</t>
+        </is>
+      </c>
+      <c r="W20" s="2" t="inlineStr">
+        <is>
           <t>99,71%</t>
-        </is>
-      </c>
-      <c r="Q20" s="2" t="inlineStr">
-        <is>
-          <t>1300</t>
-        </is>
-      </c>
-      <c r="R20" s="2" t="inlineStr">
-        <is>
-          <t>1366666</t>
-        </is>
-      </c>
-      <c r="S20" s="2" t="inlineStr">
-        <is>
-          <t>1359874</t>
-        </is>
-      </c>
-      <c r="T20" s="2" t="inlineStr">
-        <is>
-          <t>1371707</t>
-        </is>
-      </c>
-      <c r="U20" s="2" t="inlineStr">
-        <is>
-          <t>99,39%</t>
-        </is>
-      </c>
-      <c r="V20" s="2" t="inlineStr">
-        <is>
-          <t>98,9%</t>
-        </is>
-      </c>
-      <c r="W20" s="2" t="inlineStr">
-        <is>
-          <t>99,76%</t>
         </is>
       </c>
     </row>
@@ -2789,12 +2789,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>28408</t>
+          <t>29059</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>54953</t>
+          <t>55545</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2804,12 +2804,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2824,12 +2824,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>31112</t>
+          <t>31559</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>59508</t>
+          <t>56555</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2839,12 +2839,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2859,12 +2859,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>65612</t>
+          <t>67124</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>102428</t>
+          <t>103086</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2874,12 +2874,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,48%</t>
         </is>
       </c>
     </row>
@@ -2902,12 +2902,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3366957</t>
+          <t>3366365</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3393502</t>
+          <t>3392851</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2917,12 +2917,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>98,39%</t>
+          <t>98,38%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>99,17%</t>
+          <t>99,15%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2937,12 +2937,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3486224</t>
+          <t>3489177</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3514620</t>
+          <t>3514173</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2952,12 +2952,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>98,32%</t>
+          <t>98,4%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>99,12%</t>
+          <t>99,11%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2972,12 +2972,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6865214</t>
+          <t>6864556</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6902030</t>
+          <t>6900518</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2987,12 +2987,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>98,53%</t>
+          <t>98,52%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>99,06%</t>
+          <t>99,04%</t>
         </is>
       </c>
     </row>
@@ -3171,7 +3171,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de úlcera de estómago en 2016</t>
+          <t>Población con diagnóstico de úlcera de estómago en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3366,82 +3366,82 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>2014</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>2075</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>7002</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>0,58%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>0,48%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>2,02%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="R4" s="2" t="inlineStr">
         <is>
           <t>2014</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr">
+      <c r="S4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>7148</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>0,58%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>2,06%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>2014</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>7041</t>
+          <t>7044</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3479,12 +3479,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>427017</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>429092</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>99,52%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3514,7 +3514,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>339907</t>
+          <t>340053</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -3529,7 +3529,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>97,94%</t>
+          <t>97,98%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -3549,7 +3549,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>769106</t>
+          <t>769103</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -3714,7 +3714,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>7532</t>
+          <t>8862</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3729,7 +3729,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3744,62 +3744,62 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>2152</t>
+        </is>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>7645</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>0,29%</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>0,54%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>2152</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>7595</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>0,29%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,02%</t>
         </is>
       </c>
     </row>
@@ -3822,7 +3822,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>369695</t>
+          <t>368365</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -3837,7 +3837,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,0%</t>
+          <t>97,65%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -3857,12 +3857,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>370249</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>372273</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3872,12 +3872,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>99,46%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3892,7 +3892,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>741905</t>
+          <t>741855</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -3907,7 +3907,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,99%</t>
+          <t>98,98%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -4057,7 +4057,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>4293</t>
+          <t>5352</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4072,7 +4072,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4092,7 +4092,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>6123</t>
+          <t>5343</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4107,7 +4107,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4127,7 +4127,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>6769</t>
+          <t>7242</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4142,7 +4142,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>1,05%</t>
         </is>
       </c>
     </row>
@@ -4165,7 +4165,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>517621</t>
+          <t>516562</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -4180,7 +4180,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>99,18%</t>
+          <t>98,97%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -4200,7 +4200,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>160000</t>
+          <t>160780</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -4215,7 +4215,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>96,31%</t>
+          <t>96,78%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -4235,7 +4235,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>681267</t>
+          <t>680794</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -4250,7 +4250,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>99,02%</t>
+          <t>98,95%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -4395,12 +4395,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3875</t>
+          <t>4198</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>15474</t>
+          <t>16571</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4410,12 +4410,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4430,12 +4430,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>4704</t>
+          <t>4037</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>17201</t>
+          <t>17068</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4445,12 +4445,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>10717</t>
+          <t>10387</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>27945</t>
+          <t>27618</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4480,12 +4480,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,4%</t>
         </is>
       </c>
     </row>
@@ -4508,12 +4508,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1134164</t>
+          <t>1133067</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1145763</t>
+          <t>1145440</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4523,12 +4523,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>98,65%</t>
+          <t>98,56%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,66%</t>
+          <t>99,63%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4543,12 +4543,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>808675</t>
+          <t>808808</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>821172</t>
+          <t>821839</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4558,12 +4558,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>97,92%</t>
+          <t>97,93%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,43%</t>
+          <t>99,51%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4578,12 +4578,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1947569</t>
+          <t>1947896</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1964797</t>
+          <t>1965127</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4593,12 +4593,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,59%</t>
+          <t>98,6%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,46%</t>
+          <t>99,47%</t>
         </is>
       </c>
     </row>
@@ -4738,12 +4738,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1050</t>
+          <t>1046</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>10799</t>
+          <t>10446</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4758,7 +4758,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4773,12 +4773,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>3336</t>
+          <t>3261</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>17563</t>
+          <t>16788</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4788,47 +4788,47 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
+          <t>0,44%</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>2,27%</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
+          <t>12325</t>
+        </is>
+      </c>
+      <c r="S16" s="2" t="inlineStr">
+        <is>
+          <t>6144</t>
+        </is>
+      </c>
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>22384</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>0,91%</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
           <t>0,45%</t>
         </is>
       </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>2,38%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>12325</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>5675</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>22091</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>0,91%</t>
-        </is>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>0,42%</t>
-        </is>
-      </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,65%</t>
         </is>
       </c>
     </row>
@@ -4851,12 +4851,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>609907</t>
+          <t>610260</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>619656</t>
+          <t>619660</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4866,7 +4866,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>98,26%</t>
+          <t>98,32%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -4886,12 +4886,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>720681</t>
+          <t>721456</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>734908</t>
+          <t>734983</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4901,47 +4901,47 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>97,62%</t>
+          <t>97,73%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
+          <t>99,56%</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr">
+        <is>
+          <t>1286</t>
+        </is>
+      </c>
+      <c r="R17" s="2" t="inlineStr">
+        <is>
+          <t>1346625</t>
+        </is>
+      </c>
+      <c r="S17" s="2" t="inlineStr">
+        <is>
+          <t>1336566</t>
+        </is>
+      </c>
+      <c r="T17" s="2" t="inlineStr">
+        <is>
+          <t>1352806</t>
+        </is>
+      </c>
+      <c r="U17" s="2" t="inlineStr">
+        <is>
+          <t>99,09%</t>
+        </is>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
+          <t>98,35%</t>
+        </is>
+      </c>
+      <c r="W17" s="2" t="inlineStr">
+        <is>
           <t>99,55%</t>
-        </is>
-      </c>
-      <c r="Q17" s="2" t="inlineStr">
-        <is>
-          <t>1286</t>
-        </is>
-      </c>
-      <c r="R17" s="2" t="inlineStr">
-        <is>
-          <t>1346625</t>
-        </is>
-      </c>
-      <c r="S17" s="2" t="inlineStr">
-        <is>
-          <t>1336859</t>
-        </is>
-      </c>
-      <c r="T17" s="2" t="inlineStr">
-        <is>
-          <t>1353275</t>
-        </is>
-      </c>
-      <c r="U17" s="2" t="inlineStr">
-        <is>
-          <t>99,09%</t>
-        </is>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>98,37%</t>
-        </is>
-      </c>
-      <c r="W17" s="2" t="inlineStr">
-        <is>
-          <t>99,58%</t>
         </is>
       </c>
     </row>
@@ -5081,12 +5081,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5096,12 +5096,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>6592</t>
+          <t>7196</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>22467</t>
+          <t>23817</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5131,12 +5131,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5151,12 +5151,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>7423</t>
+          <t>7329</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>23162</t>
+          <t>23143</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5194,12 +5194,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>285126</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>287145</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5209,12 +5209,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>99,3%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5229,12 +5229,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1059558</t>
+          <t>1058208</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1075433</t>
+          <t>1074829</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5244,12 +5244,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>97,92%</t>
+          <t>97,8%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>99,39%</t>
+          <t>99,33%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5264,12 +5264,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1346008</t>
+          <t>1346027</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1361747</t>
+          <t>1361841</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5424,12 +5424,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>9004</t>
+          <t>9099</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>25406</t>
+          <t>25568</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5444,7 +5444,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5459,12 +5459,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>24257</t>
+          <t>24198</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>48788</t>
+          <t>48926</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5479,7 +5479,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5494,12 +5494,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>36418</t>
+          <t>35882</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>67584</t>
+          <t>65284</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5509,12 +5509,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>0,94%</t>
         </is>
       </c>
     </row>
@@ -5537,12 +5537,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3360316</t>
+          <t>3360154</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3376718</t>
+          <t>3376623</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5552,7 +5552,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>99,25%</t>
+          <t>99,24%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -5572,12 +5572,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3482808</t>
+          <t>3482670</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3507339</t>
+          <t>3507398</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5587,7 +5587,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>98,62%</t>
+          <t>98,61%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -5607,12 +5607,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6849734</t>
+          <t>6852034</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6880900</t>
+          <t>6881436</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5622,12 +5622,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>99,02%</t>
+          <t>99,06%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>99,47%</t>
+          <t>99,48%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P1406-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P1406-Clase-trans_orig.xlsx
@@ -736,7 +736,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>7438</t>
+          <t>7401</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -751,7 +751,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -771,7 +771,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>6017</t>
+          <t>6722</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -786,7 +786,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -801,12 +801,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1001</t>
+          <t>995</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>9818</t>
+          <t>10689</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -821,7 +821,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,42%</t>
         </is>
       </c>
     </row>
@@ -844,7 +844,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>429773</t>
+          <t>429810</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -859,7 +859,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>98,3%</t>
+          <t>98,31%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -879,7 +879,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>308437</t>
+          <t>307732</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -894,7 +894,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>98,09%</t>
+          <t>97,86%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -914,12 +914,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>741847</t>
+          <t>740976</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>750664</t>
+          <t>750670</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -929,7 +929,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,69%</t>
+          <t>98,58%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -1079,7 +1079,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>11300</t>
+          <t>10803</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1094,7 +1094,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>968</t>
+          <t>982</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>13382</t>
+          <t>12604</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1129,7 +1129,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>3,73%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1144,12 +1144,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>4077</t>
+          <t>4069</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>19445</t>
+          <t>17694</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1164,7 +1164,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,34%</t>
         </is>
       </c>
     </row>
@@ -1187,7 +1187,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>407497</t>
+          <t>407994</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,3%</t>
+          <t>97,42%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1222,12 +1222,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>324629</t>
+          <t>325407</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>337043</t>
+          <t>337029</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1237,7 +1237,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>96,04%</t>
+          <t>96,27%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1257,12 +1257,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>737363</t>
+          <t>739114</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>752731</t>
+          <t>752739</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1272,7 +1272,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,43%</t>
+          <t>97,66%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1054</t>
+          <t>1063</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>9557</t>
+          <t>9509</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1437,7 +1437,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1457,7 +1457,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>6846</t>
+          <t>7368</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1472,7 +1472,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1487,12 +1487,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2231</t>
+          <t>2238</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>12876</t>
+          <t>13647</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1507,7 +1507,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,53%</t>
         </is>
       </c>
     </row>
@@ -1530,12 +1530,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>619858</t>
+          <t>619906</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>628361</t>
+          <t>628352</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1545,7 +1545,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>98,48%</t>
+          <t>98,49%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1565,7 +1565,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>253283</t>
+          <t>252761</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -1580,7 +1580,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>97,37%</t>
+          <t>97,17%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1600,12 +1600,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>876668</t>
+          <t>875897</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>887313</t>
+          <t>887306</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1615,7 +1615,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,55%</t>
+          <t>98,47%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1760,12 +1760,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>14077</t>
+          <t>14837</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>33748</t>
+          <t>36315</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1775,12 +1775,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1795,12 +1795,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>5559</t>
+          <t>5506</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>21013</t>
+          <t>19877</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1810,12 +1810,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1830,12 +1830,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>23884</t>
+          <t>23471</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>49684</t>
+          <t>48781</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1845,12 +1845,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,54%</t>
         </is>
       </c>
     </row>
@@ -1873,12 +1873,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1125261</t>
+          <t>1122694</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1144932</t>
+          <t>1144172</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1888,12 +1888,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,09%</t>
+          <t>96,87%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,79%</t>
+          <t>98,72%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1908,12 +1908,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>743709</t>
+          <t>744845</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>759163</t>
+          <t>759216</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1923,12 +1923,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>97,25%</t>
+          <t>97,4%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,27%</t>
+          <t>99,28%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1943,12 +1943,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1874047</t>
+          <t>1874950</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1899847</t>
+          <t>1900260</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1958,12 +1958,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,42%</t>
+          <t>97,46%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,76%</t>
+          <t>98,78%</t>
         </is>
       </c>
     </row>
@@ -2103,12 +2103,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2935</t>
+          <t>2139</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>13893</t>
+          <t>12775</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2118,12 +2118,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2138,12 +2138,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>8545</t>
+          <t>8581</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>24349</t>
+          <t>23717</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2153,12 +2153,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2173,12 +2173,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>13441</t>
+          <t>13570</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>31383</t>
+          <t>31514</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2188,12 +2188,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,48%</t>
         </is>
       </c>
     </row>
@@ -2216,12 +2216,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>496703</t>
+          <t>497821</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>507661</t>
+          <t>508457</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2231,12 +2231,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>97,28%</t>
+          <t>97,5%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,43%</t>
+          <t>99,58%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2251,12 +2251,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>735897</t>
+          <t>736529</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>751701</t>
+          <t>751665</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2266,12 +2266,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>96,8%</t>
+          <t>96,88%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>98,88%</t>
+          <t>98,87%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2286,12 +2286,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1239460</t>
+          <t>1239329</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1257402</t>
+          <t>1257273</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2301,12 +2301,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>97,53%</t>
+          <t>97,52%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,94%</t>
+          <t>98,93%</t>
         </is>
       </c>
     </row>
@@ -2426,7 +2426,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2481,12 +2481,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>4105</t>
+          <t>4080</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>16061</t>
+          <t>15745</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2501,7 +2501,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2516,12 +2516,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>3982</t>
+          <t>4010</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>15303</t>
+          <t>16756</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2536,7 +2536,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,22%</t>
         </is>
       </c>
     </row>
@@ -2594,12 +2594,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1092108</t>
+          <t>1092424</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1104064</t>
+          <t>1104089</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2609,7 +2609,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>98,55%</t>
+          <t>98,58%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2629,12 +2629,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1359748</t>
+          <t>1358295</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1371069</t>
+          <t>1371041</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2644,7 +2644,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>98,89%</t>
+          <t>98,78%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -2789,12 +2789,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>29059</t>
+          <t>27664</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>55545</t>
+          <t>55654</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2804,12 +2804,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2824,12 +2824,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>31559</t>
+          <t>30496</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>56555</t>
+          <t>58495</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2839,12 +2839,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2859,12 +2859,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>67124</t>
+          <t>66507</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>103086</t>
+          <t>104419</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2874,12 +2874,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,5%</t>
         </is>
       </c>
     </row>
@@ -2902,12 +2902,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3366365</t>
+          <t>3366256</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3392851</t>
+          <t>3394246</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2917,12 +2917,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>98,38%</t>
+          <t>98,37%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>99,15%</t>
+          <t>99,19%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2937,12 +2937,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3489177</t>
+          <t>3487237</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3514173</t>
+          <t>3515236</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2952,12 +2952,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>98,4%</t>
+          <t>98,35%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>99,11%</t>
+          <t>99,14%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2972,12 +2972,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6864556</t>
+          <t>6863223</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6900518</t>
+          <t>6901135</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2987,12 +2987,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>98,52%</t>
+          <t>98,5%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>99,04%</t>
+          <t>99,05%</t>
         </is>
       </c>
     </row>
@@ -3406,7 +3406,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>7002</t>
+          <t>6961</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3421,7 +3421,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3441,7 +3441,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>7044</t>
+          <t>7201</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3456,7 +3456,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,93%</t>
         </is>
       </c>
     </row>
@@ -3514,7 +3514,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>340053</t>
+          <t>340094</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -3529,7 +3529,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>97,98%</t>
+          <t>97,99%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -3549,7 +3549,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>769103</t>
+          <t>768946</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -3564,7 +3564,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>99,09%</t>
+          <t>99,07%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -3714,7 +3714,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>8862</t>
+          <t>7203</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3729,7 +3729,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3784,7 +3784,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>7645</t>
+          <t>8118</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3799,7 +3799,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,08%</t>
         </is>
       </c>
     </row>
@@ -3822,7 +3822,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>368365</t>
+          <t>370024</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -3837,7 +3837,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,65%</t>
+          <t>98,09%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -3892,7 +3892,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>741855</t>
+          <t>741382</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -3907,7 +3907,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,98%</t>
+          <t>98,92%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -4057,7 +4057,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>5352</t>
+          <t>5234</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4072,7 +4072,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4092,7 +4092,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>5343</t>
+          <t>5901</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4107,7 +4107,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,55%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4127,7 +4127,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>7242</t>
+          <t>6750</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4142,7 +4142,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>0,98%</t>
         </is>
       </c>
     </row>
@@ -4165,7 +4165,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>516562</t>
+          <t>516680</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -4180,7 +4180,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>98,97%</t>
+          <t>99,0%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -4200,7 +4200,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>160780</t>
+          <t>160222</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -4215,7 +4215,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>96,78%</t>
+          <t>96,45%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -4235,7 +4235,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>680794</t>
+          <t>681286</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -4250,7 +4250,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,95%</t>
+          <t>99,02%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -4395,12 +4395,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4198</t>
+          <t>3450</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>16571</t>
+          <t>16054</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4410,12 +4410,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4430,12 +4430,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>4037</t>
+          <t>4319</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>17068</t>
+          <t>17089</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4445,7 +4445,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>10387</t>
+          <t>10366</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>27618</t>
+          <t>27707</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4480,7 +4480,7 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -4508,12 +4508,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1133067</t>
+          <t>1133584</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1145440</t>
+          <t>1146188</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4523,12 +4523,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>98,56%</t>
+          <t>98,6%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,63%</t>
+          <t>99,7%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4543,12 +4543,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>808808</t>
+          <t>808787</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>821839</t>
+          <t>821557</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4563,7 +4563,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,51%</t>
+          <t>99,48%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4578,12 +4578,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1947896</t>
+          <t>1947807</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1965127</t>
+          <t>1965148</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4598,7 +4598,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,47%</t>
+          <t>99,48%</t>
         </is>
       </c>
     </row>
@@ -4738,12 +4738,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1046</t>
+          <t>1049</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>10446</t>
+          <t>11775</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4758,7 +4758,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4773,12 +4773,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>3261</t>
+          <t>3961</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>16788</t>
+          <t>16875</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4788,12 +4788,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4808,12 +4808,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>6144</t>
+          <t>6192</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>22384</t>
+          <t>22320</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4823,12 +4823,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,64%</t>
         </is>
       </c>
     </row>
@@ -4851,12 +4851,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>610260</t>
+          <t>608931</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>619660</t>
+          <t>619657</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4866,7 +4866,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>98,32%</t>
+          <t>98,1%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -4886,12 +4886,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>721456</t>
+          <t>721369</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>734983</t>
+          <t>734283</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4901,12 +4901,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>97,73%</t>
+          <t>97,71%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,56%</t>
+          <t>99,46%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4921,12 +4921,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1336566</t>
+          <t>1336630</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1352806</t>
+          <t>1352758</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4936,12 +4936,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>98,35%</t>
+          <t>98,36%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,55%</t>
+          <t>99,54%</t>
         </is>
       </c>
     </row>
@@ -5061,7 +5061,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>7196</t>
+          <t>7307</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>23817</t>
+          <t>23439</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5131,12 +5131,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5151,12 +5151,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>7329</t>
+          <t>6949</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>23143</t>
+          <t>22459</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5166,12 +5166,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,64%</t>
         </is>
       </c>
     </row>
@@ -5229,12 +5229,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1058208</t>
+          <t>1058586</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1074829</t>
+          <t>1074718</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5244,12 +5244,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>97,8%</t>
+          <t>97,83%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>99,33%</t>
+          <t>99,32%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5264,12 +5264,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1346027</t>
+          <t>1346711</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1361841</t>
+          <t>1362221</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5279,12 +5279,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>98,31%</t>
+          <t>98,36%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>99,46%</t>
+          <t>99,49%</t>
         </is>
       </c>
     </row>
@@ -5424,12 +5424,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>9099</t>
+          <t>8415</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>25568</t>
+          <t>25412</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5439,12 +5439,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5459,12 +5459,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>24198</t>
+          <t>23497</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>48926</t>
+          <t>48142</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5474,12 +5474,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5494,12 +5494,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>35882</t>
+          <t>37335</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>65284</t>
+          <t>65855</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5509,12 +5509,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,95%</t>
         </is>
       </c>
     </row>
@@ -5537,12 +5537,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3360154</t>
+          <t>3360310</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3376623</t>
+          <t>3377307</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5552,12 +5552,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>99,24%</t>
+          <t>99,25%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>99,73%</t>
+          <t>99,75%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5572,12 +5572,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3482670</t>
+          <t>3483454</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3507398</t>
+          <t>3508099</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5587,12 +5587,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>98,61%</t>
+          <t>98,64%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>99,31%</t>
+          <t>99,33%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5607,12 +5607,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6852034</t>
+          <t>6851463</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6881436</t>
+          <t>6879983</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5622,12 +5622,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>99,06%</t>
+          <t>99,05%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>99,48%</t>
+          <t>99,46%</t>
         </is>
       </c>
     </row>
